--- a/__tests__/fixtures/ventas_simple.xlsx
+++ b/__tests__/fixtures/ventas_simple.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="17">
   <si>
-    <t>Mes</t>
+    <t>Fecha</t>
   </si>
   <si>
     <t>Total</t>
